--- a/Docs/EnemySheets.xlsx
+++ b/Docs/EnemySheets.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50C8B1B-A3B6-4AE1-85F1-45493ECB0C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="32" r:id="rId1"/>

--- a/Docs/EnemySheets.xlsx
+++ b/Docs/EnemySheets.xlsx
@@ -1254,7 +1254,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>6</v>
@@ -3013,7 +3013,7 @@
         <v>180</v>
       </c>
       <c r="B8" s="0">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -9493,7 +9493,7 @@
         <v>180</v>
       </c>
       <c r="B8" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -14179,7 +14179,7 @@
         <v>89</v>
       </c>
       <c r="E5" s="0">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F5" s="0">
         <v>1</v>
@@ -14241,7 +14241,7 @@
         <v>235</v>
       </c>
       <c r="E6" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F6" s="0">
         <v>1</v>
@@ -14489,7 +14489,7 @@
         <v>248</v>
       </c>
       <c r="E10" s="0">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F10" s="0">
         <v>1</v>
@@ -15047,7 +15047,7 @@
         <v>272</v>
       </c>
       <c r="E19" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F19" s="0">
         <v>1</v>
@@ -17930,7 +17930,7 @@
         <v>180</v>
       </c>
       <c r="B8" s="0">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -18740,7 +18740,7 @@
         <v>180</v>
       </c>
       <c r="B8" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
